--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ139"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17783,57 +17783,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>110017543</v>
+        <v>136624956</v>
       </c>
       <c r="B136" t="n">
-        <v>43438</v>
+        <v>43457</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>101298</v>
+        <v>100942</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Södra ledningsgatan, Siggefora, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>620824</v>
+        <v>620777</v>
       </c>
       <c r="R136" t="n">
-        <v>6650727</v>
+        <v>6650974</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17857,12 +17857,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17871,85 +17871,85 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Mikael Åsberg</t>
+          <t>Milad Avalinejad Bandari</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110017543</t>
+          <t>https://artportalen.se/Sighting/136624956</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>110016422</v>
+        <v>136624962</v>
       </c>
       <c r="B137" t="n">
-        <v>58039</v>
+        <v>43457</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>102626</v>
+        <v>100942</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Södra ledningsgatan, Siggefora, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>620810</v>
+        <v>620780</v>
       </c>
       <c r="R137" t="n">
-        <v>6650785</v>
+        <v>6651005</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17973,12 +17973,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17987,96 +17987,85 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Mikael Åsberg</t>
+          <t>Milad Avalinejad Bandari</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110016422</t>
+          <t>https://artportalen.se/Sighting/136624962</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130715501</v>
+        <v>136624963</v>
       </c>
       <c r="B138" t="n">
-        <v>5362</v>
+        <v>43457</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>105947</v>
+        <v>100942</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Större aspvedbock</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Saperda carcharias</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Siggefora, kraftledningsgatan, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>620786</v>
+        <v>620775</v>
       </c>
       <c r="R138" t="n">
-        <v>6651017</v>
+        <v>6651011</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -18100,12 +18089,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18121,27 +18110,31 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Milad Avalinejad Bandari</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Rasmus Elleby, Jon Jörpeland</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130715501</t>
+          <t>https://artportalen.se/Sighting/136624963</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>60228648</v>
+        <v>136624968</v>
       </c>
       <c r="B139" t="n">
-        <v>43378</v>
+        <v>43457</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18149,54 +18142,46 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>201075</v>
+        <v>100942</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Siggeforasjön, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>620769</v>
+        <v>620770</v>
       </c>
       <c r="R139" t="n">
-        <v>6650998</v>
+        <v>6651009</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -18220,12 +18205,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18234,22 +18219,617 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624968</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>136624970</v>
+      </c>
+      <c r="B140" t="n">
+        <v>43457</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>620770</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6651006</v>
+      </c>
+      <c r="S140" t="n">
+        <v>8</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624970</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>110017543</v>
+      </c>
+      <c r="B141" t="n">
+        <v>43438</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>101298</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Melitaea diamina</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Södra ledningsgatan, Siggefora, Upl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>620824</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6650727</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110017543</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>110016422</v>
+      </c>
+      <c r="B142" t="n">
+        <v>58039</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Södra ledningsgatan, Siggefora, Upl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>620810</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6650785</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110016422</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>130715501</v>
+      </c>
+      <c r="B143" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>105947</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Större aspvedbock</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Saperda carcharias</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Siggefora, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>620786</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6651017</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby, Jon Jörpeland</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130715501</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>60228648</v>
+      </c>
+      <c r="B144" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Siggeforasjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>620769</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6650998</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2016-06-20</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2016-06-20</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
           <t>Göran Frisk</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>Göran Frisk, Kristina Nygren Frisk</t>
         </is>
       </c>
-      <c r="AY139" t="inlineStr"/>
-      <c r="AZ139" t="inlineStr">
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/60228648</t>
         </is>
@@ -18395,6 +18975,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -18178,7 +18178,7 @@
         <v>620770</v>
       </c>
       <c r="R139" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S139" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -18178,7 +18178,7 @@
         <v>620770</v>
       </c>
       <c r="R139" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S139" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -17786,7 +17786,7 @@
         <v>136624956</v>
       </c>
       <c r="B136" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>136624962</v>
       </c>
       <c r="B137" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>136624963</v>
       </c>
       <c r="B138" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>136624968</v>
       </c>
       <c r="B139" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>136624970</v>
       </c>
       <c r="B140" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ144"/>
+  <dimension ref="A1:AZ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,73 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109823498</v>
+        <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>40614</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskäreplattmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agonopterix bipunctosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Curtis, 1850)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Siggefora, kraftledningsgata, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620777</v>
+        <v>620919</v>
       </c>
       <c r="R2" t="n">
-        <v>6650986</v>
+        <v>6650785</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I hopspunna blad på ängsskära.</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,86 +769,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109823498</t>
+          <t>https://artportalen.se/Sighting/136866751</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110098083</v>
+        <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>40614</v>
+        <v>96688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100204</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsskäreplattmal</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agonopterix bipunctosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Curtis, 1850)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Siggefora kraftledningsgata, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620788</v>
+        <v>620896</v>
       </c>
       <c r="R3" t="n">
-        <v>6650998</v>
+        <v>6651061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,90 +881,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Björkén</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110098083</t>
+          <t>https://artportalen.se/Sighting/136866741</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120777197</v>
+        <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>43426</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100942</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620774</v>
+        <v>620848</v>
       </c>
       <c r="R4" t="n">
-        <v>6650983</v>
+        <v>6651036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1019,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,81 +993,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777197</t>
+          <t>https://artportalen.se/Sighting/136866742</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14576239</v>
+        <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>43426</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100942</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620809</v>
+        <v>620819</v>
       </c>
       <c r="R5" t="n">
-        <v>6650830</v>
+        <v>6650971</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,17 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 larvkoloni</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,78 +1108,68 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14576239</t>
+          <t>https://artportalen.se/Sighting/136866744</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14576245</v>
+        <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>43426</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100942</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620812</v>
+        <v>620957</v>
       </c>
       <c r="R6" t="n">
-        <v>6650773</v>
+        <v>6650789</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,17 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 larvkolonier</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,78 +1220,73 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14576245</t>
+          <t>https://artportalen.se/Sighting/136866746</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14576250</v>
+        <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>43426</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100942</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620781</v>
+        <v>620911</v>
       </c>
       <c r="R7" t="n">
-        <v>6650935</v>
+        <v>6650795</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,17 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 larvkolonier</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,35 +1337,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14576250</t>
+          <t>https://artportalen.se/Sighting/136866752</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14576251</v>
+        <v>109823498</v>
       </c>
       <c r="B8" t="n">
-        <v>43426</v>
+        <v>40614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,24 +1368,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100942</v>
+        <v>100204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Ängsskäreplattmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Agonopterix bipunctosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Curtis, 1850)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1448,17 +1413,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
+          <t>Siggefora, kraftledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620783</v>
+        <v>620777</v>
       </c>
       <c r="R8" t="n">
-        <v>6650929</v>
+        <v>6650986</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,17 +1447,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-09-10</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 larvkolonier</t>
+          <t>I hopspunna blad på ängsskära.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,38 +1466,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Moa Pettersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14576251</t>
+          <t>https://artportalen.se/Sighting/109823498</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62246076</v>
+        <v>110098083</v>
       </c>
       <c r="B9" t="n">
-        <v>43426</v>
+        <v>40614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100942</v>
+        <v>100204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Ängsskäreplattmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Agonopterix bipunctosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Curtis, 1850)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1564,7 +1525,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kolonier</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1574,24 +1535,20 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Siggefora kraftledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620781</v>
+        <v>620788</v>
       </c>
       <c r="R9" t="n">
-        <v>6650933</v>
+        <v>6650998</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,12 +1572,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,93 +1586,69 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Anders Björkén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Anders Björkén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246076</t>
+          <t>https://artportalen.se/Sighting/110098083</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62246183</v>
+        <v>136866753</v>
       </c>
       <c r="B10" t="n">
-        <v>43426</v>
+        <v>5182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100942</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Östfora, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620768</v>
+        <v>620908</v>
       </c>
       <c r="R10" t="n">
-        <v>6651007</v>
+        <v>6650745</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1742,12 +1675,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,28 +1705,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246183</t>
+          <t>https://artportalen.se/Sighting/136866753</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62246185</v>
+        <v>120777197</v>
       </c>
       <c r="B11" t="n">
         <v>43426</v>
@@ -1839,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620781</v>
+        <v>620774</v>
       </c>
       <c r="R11" t="n">
-        <v>6650929</v>
+        <v>6650983</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1869,12 +1808,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,6 +1822,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1904,13 +1844,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246185</t>
+          <t>https://artportalen.se/Sighting/120777197</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62246187</v>
+        <v>14576239</v>
       </c>
       <c r="B12" t="n">
         <v>43426</v>
@@ -1938,23 +1878,7 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1962,17 +1886,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620814</v>
+        <v>620809</v>
       </c>
       <c r="R12" t="n">
-        <v>6650775</v>
+        <v>6650830</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1996,12 +1920,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 larvkoloni</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,31 +1942,32 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246187</t>
+          <t>https://artportalen.se/Sighting/14576239</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>62246188</v>
+        <v>14576245</v>
       </c>
       <c r="B13" t="n">
         <v>43426</v>
@@ -2065,23 +1995,7 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2089,17 +2003,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620816</v>
+        <v>620812</v>
       </c>
       <c r="R13" t="n">
         <v>6650773</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2123,12 +2037,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 larvkolonier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,31 +2059,32 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246188</t>
+          <t>https://artportalen.se/Sighting/14576245</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62246189</v>
+        <v>14576250</v>
       </c>
       <c r="B14" t="n">
         <v>43426</v>
@@ -2192,23 +2112,7 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2216,17 +2120,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620818</v>
+        <v>620781</v>
       </c>
       <c r="R14" t="n">
-        <v>6650771</v>
+        <v>6650935</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,12 +2154,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-09-11</t>
+          <t>2010-09-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 larvkolonier</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,31 +2176,32 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246189</t>
+          <t>https://artportalen.se/Sighting/14576250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62246496</v>
+        <v>14576251</v>
       </c>
       <c r="B15" t="n">
         <v>43426</v>
@@ -2319,23 +2229,7 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2343,17 +2237,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Kraftledningsgatan vid Blackbo O Siggeforasjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620828</v>
+        <v>620783</v>
       </c>
       <c r="R15" t="n">
-        <v>6650768</v>
+        <v>6650929</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,12 +2271,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2010-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2010-09-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3 larvkolonier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,31 +2293,32 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Via Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246496</t>
+          <t>https://artportalen.se/Sighting/14576251</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62246502</v>
+        <v>62246076</v>
       </c>
       <c r="B16" t="n">
         <v>43426</v>
@@ -2474,10 +2374,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620780</v>
+        <v>620781</v>
       </c>
       <c r="R16" t="n">
-        <v>6650986</v>
+        <v>6650933</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2504,12 +2404,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2539,13 +2439,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246502</t>
+          <t>https://artportalen.se/Sighting/62246076</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62246507</v>
+        <v>62246183</v>
       </c>
       <c r="B17" t="n">
         <v>43426</v>
@@ -2601,10 +2501,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620839</v>
+        <v>620768</v>
       </c>
       <c r="R17" t="n">
-        <v>6650749</v>
+        <v>6651007</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2631,12 +2531,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2666,13 +2566,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62246507</t>
+          <t>https://artportalen.se/Sighting/62246183</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62247252</v>
+        <v>62246185</v>
       </c>
       <c r="B18" t="n">
         <v>43426</v>
@@ -2728,10 +2628,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620821</v>
+        <v>620781</v>
       </c>
       <c r="R18" t="n">
-        <v>6650774</v>
+        <v>6650929</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2758,12 +2658,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2793,13 +2693,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247252</t>
+          <t>https://artportalen.se/Sighting/62246185</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>62247253</v>
+        <v>62246187</v>
       </c>
       <c r="B19" t="n">
         <v>43426</v>
@@ -2855,10 +2755,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620835</v>
+        <v>620814</v>
       </c>
       <c r="R19" t="n">
-        <v>6650759</v>
+        <v>6650775</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2885,12 +2785,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2920,13 +2820,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247253</t>
+          <t>https://artportalen.se/Sighting/62246187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>62247254</v>
+        <v>62246188</v>
       </c>
       <c r="B20" t="n">
         <v>43426</v>
@@ -2982,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620837</v>
+        <v>620816</v>
       </c>
       <c r="R20" t="n">
-        <v>6650755</v>
+        <v>6650773</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3012,12 +2912,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,13 +2947,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247254</t>
+          <t>https://artportalen.se/Sighting/62246188</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>62247255</v>
+        <v>62246189</v>
       </c>
       <c r="B21" t="n">
         <v>43426</v>
@@ -3109,10 +3009,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620838</v>
+        <v>620818</v>
       </c>
       <c r="R21" t="n">
-        <v>6650756</v>
+        <v>6650771</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3139,12 +3039,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3174,13 +3074,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247255</t>
+          <t>https://artportalen.se/Sighting/62246189</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62247257</v>
+        <v>62246496</v>
       </c>
       <c r="B22" t="n">
         <v>43426</v>
@@ -3239,7 +3139,7 @@
         <v>620828</v>
       </c>
       <c r="R22" t="n">
-        <v>6650784</v>
+        <v>6650768</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3266,12 +3166,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3301,13 +3201,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247257</t>
+          <t>https://artportalen.se/Sighting/62246496</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>62247258</v>
+        <v>62246502</v>
       </c>
       <c r="B23" t="n">
         <v>43426</v>
@@ -3363,10 +3263,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620797</v>
+        <v>620780</v>
       </c>
       <c r="R23" t="n">
-        <v>6650944</v>
+        <v>6650986</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3393,12 +3293,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3428,13 +3328,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247258</t>
+          <t>https://artportalen.se/Sighting/62246502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62247265</v>
+        <v>62246507</v>
       </c>
       <c r="B24" t="n">
         <v>43426</v>
@@ -3490,10 +3390,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620783</v>
+        <v>620839</v>
       </c>
       <c r="R24" t="n">
-        <v>6650933</v>
+        <v>6650749</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3520,12 +3420,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,13 +3455,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247265</t>
+          <t>https://artportalen.se/Sighting/62246507</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>62247266</v>
+        <v>62247252</v>
       </c>
       <c r="B25" t="n">
         <v>43426</v>
@@ -3617,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620775</v>
+        <v>620821</v>
       </c>
       <c r="R25" t="n">
-        <v>6650982</v>
+        <v>6650774</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3682,13 +3582,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247266</t>
+          <t>https://artportalen.se/Sighting/62247252</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>62247267</v>
+        <v>62247253</v>
       </c>
       <c r="B26" t="n">
         <v>43426</v>
@@ -3744,10 +3644,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620775</v>
+        <v>620835</v>
       </c>
       <c r="R26" t="n">
-        <v>6650978</v>
+        <v>6650759</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3809,13 +3709,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247267</t>
+          <t>https://artportalen.se/Sighting/62247253</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>62247268</v>
+        <v>62247254</v>
       </c>
       <c r="B27" t="n">
         <v>43426</v>
@@ -3871,10 +3771,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620775</v>
+        <v>620837</v>
       </c>
       <c r="R27" t="n">
-        <v>6650976</v>
+        <v>6650755</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3936,13 +3836,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247268</t>
+          <t>https://artportalen.se/Sighting/62247254</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>62247269</v>
+        <v>62247255</v>
       </c>
       <c r="B28" t="n">
         <v>43426</v>
@@ -3998,10 +3898,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620768</v>
+        <v>620838</v>
       </c>
       <c r="R28" t="n">
-        <v>6651004</v>
+        <v>6650756</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4063,13 +3963,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247269</t>
+          <t>https://artportalen.se/Sighting/62247255</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>62247270</v>
+        <v>62247257</v>
       </c>
       <c r="B29" t="n">
         <v>43426</v>
@@ -4125,10 +4025,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620766</v>
+        <v>620828</v>
       </c>
       <c r="R29" t="n">
-        <v>6651010</v>
+        <v>6650784</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4190,13 +4090,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247270</t>
+          <t>https://artportalen.se/Sighting/62247257</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62247271</v>
+        <v>62247258</v>
       </c>
       <c r="B30" t="n">
         <v>43426</v>
@@ -4252,10 +4152,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620768</v>
+        <v>620797</v>
       </c>
       <c r="R30" t="n">
-        <v>6651011</v>
+        <v>6650944</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4317,13 +4217,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247271</t>
+          <t>https://artportalen.se/Sighting/62247258</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>62247275</v>
+        <v>62247265</v>
       </c>
       <c r="B31" t="n">
         <v>43426</v>
@@ -4379,10 +4279,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620787</v>
+        <v>620783</v>
       </c>
       <c r="R31" t="n">
-        <v>6651022</v>
+        <v>6650933</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4444,13 +4344,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62247275</t>
+          <t>https://artportalen.se/Sighting/62247265</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>66607395</v>
+        <v>62247266</v>
       </c>
       <c r="B32" t="n">
         <v>43426</v>
@@ -4483,29 +4383,33 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Siggeforasjön, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620769</v>
+        <v>620775</v>
       </c>
       <c r="R32" t="n">
-        <v>6650998</v>
+        <v>6650982</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4532,17 +4436,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2017-07-08</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2017-07-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Sliten</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4557,24 +4456,28 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Frisk</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Frisk, Kristina Nygren Frisk</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66607395</t>
+          <t>https://artportalen.se/Sighting/62247266</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>69915509</v>
+        <v>62247267</v>
       </c>
       <c r="B33" t="n">
         <v>43426</v>
@@ -4630,7 +4533,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620772</v>
+        <v>620775</v>
       </c>
       <c r="R33" t="n">
         <v>6650978</v>
@@ -4660,12 +4563,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4695,13 +4598,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915509</t>
+          <t>https://artportalen.se/Sighting/62247267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>69915510</v>
+        <v>62247268</v>
       </c>
       <c r="B34" t="n">
         <v>43426</v>
@@ -4757,10 +4660,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620776</v>
+        <v>620775</v>
       </c>
       <c r="R34" t="n">
-        <v>6650981</v>
+        <v>6650976</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4787,12 +4690,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4822,13 +4725,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915510</t>
+          <t>https://artportalen.se/Sighting/62247268</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>69915511</v>
+        <v>62247269</v>
       </c>
       <c r="B35" t="n">
         <v>43426</v>
@@ -4884,10 +4787,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620775</v>
+        <v>620768</v>
       </c>
       <c r="R35" t="n">
-        <v>6650981</v>
+        <v>6651004</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4914,12 +4817,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4949,13 +4852,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915511</t>
+          <t>https://artportalen.se/Sighting/62247269</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>69915512</v>
+        <v>62247270</v>
       </c>
       <c r="B36" t="n">
         <v>43426</v>
@@ -5011,10 +4914,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620777</v>
+        <v>620766</v>
       </c>
       <c r="R36" t="n">
-        <v>6650981</v>
+        <v>6651010</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5041,12 +4944,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5076,13 +4979,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915512</t>
+          <t>https://artportalen.se/Sighting/62247270</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69915513</v>
+        <v>62247271</v>
       </c>
       <c r="B37" t="n">
         <v>43426</v>
@@ -5138,10 +5041,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620776</v>
+        <v>620768</v>
       </c>
       <c r="R37" t="n">
-        <v>6650983</v>
+        <v>6651011</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5168,12 +5071,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5203,13 +5106,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915513</t>
+          <t>https://artportalen.se/Sighting/62247271</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>69915521</v>
+        <v>62247275</v>
       </c>
       <c r="B38" t="n">
         <v>43426</v>
@@ -5265,10 +5168,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620820</v>
+        <v>620787</v>
       </c>
       <c r="R38" t="n">
-        <v>6650771</v>
+        <v>6651022</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5295,12 +5198,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5330,13 +5233,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915521</t>
+          <t>https://artportalen.se/Sighting/62247275</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>69915522</v>
+        <v>66607395</v>
       </c>
       <c r="B39" t="n">
         <v>43426</v>
@@ -5369,33 +5272,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Siggeforasjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620811</v>
+        <v>620769</v>
       </c>
       <c r="R39" t="n">
-        <v>6650785</v>
+        <v>6650998</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5422,12 +5321,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2017-07-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2017-07-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sliten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5442,28 +5346,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Göran Frisk, Kristina Nygren Frisk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915522</t>
+          <t>https://artportalen.se/Sighting/66607395</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>69915523</v>
+        <v>69915509</v>
       </c>
       <c r="B40" t="n">
         <v>43426</v>
@@ -5519,10 +5419,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620809</v>
+        <v>620772</v>
       </c>
       <c r="R40" t="n">
-        <v>6650798</v>
+        <v>6650978</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5584,13 +5484,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69915523</t>
+          <t>https://artportalen.se/Sighting/69915509</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>80003798</v>
+        <v>69915510</v>
       </c>
       <c r="B41" t="n">
         <v>43426</v>
@@ -5646,10 +5546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620839</v>
+        <v>620776</v>
       </c>
       <c r="R41" t="n">
-        <v>6650756</v>
+        <v>6650981</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5676,12 +5576,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,7 +5590,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5712,13 +5611,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80003798</t>
+          <t>https://artportalen.se/Sighting/69915510</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>80003800</v>
+        <v>69915511</v>
       </c>
       <c r="B42" t="n">
         <v>43426</v>
@@ -5774,10 +5673,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620819</v>
+        <v>620775</v>
       </c>
       <c r="R42" t="n">
-        <v>6650773</v>
+        <v>6650981</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5804,12 +5703,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5818,7 +5717,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5840,13 +5738,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80003800</t>
+          <t>https://artportalen.se/Sighting/69915511</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>80003809</v>
+        <v>69915512</v>
       </c>
       <c r="B43" t="n">
         <v>43426</v>
@@ -5902,10 +5800,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620769</v>
+        <v>620777</v>
       </c>
       <c r="R43" t="n">
-        <v>6651010</v>
+        <v>6650981</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5932,12 +5830,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5946,7 +5844,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5968,13 +5865,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80003809</t>
+          <t>https://artportalen.se/Sighting/69915512</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80003810</v>
+        <v>69915513</v>
       </c>
       <c r="B44" t="n">
         <v>43426</v>
@@ -6030,10 +5927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620769</v>
+        <v>620776</v>
       </c>
       <c r="R44" t="n">
-        <v>6651003</v>
+        <v>6650983</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6060,12 +5957,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6074,7 +5971,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6096,13 +5992,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80003810</t>
+          <t>https://artportalen.se/Sighting/69915513</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>80009164</v>
+        <v>69915521</v>
       </c>
       <c r="B45" t="n">
         <v>43426</v>
@@ -6158,10 +6054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620845</v>
+        <v>620820</v>
       </c>
       <c r="R45" t="n">
-        <v>6650723</v>
+        <v>6650771</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6188,12 +6084,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6202,7 +6098,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6224,13 +6119,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009164</t>
+          <t>https://artportalen.se/Sighting/69915521</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>80009165</v>
+        <v>69915522</v>
       </c>
       <c r="B46" t="n">
         <v>43426</v>
@@ -6286,10 +6181,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620844</v>
+        <v>620811</v>
       </c>
       <c r="R46" t="n">
-        <v>6650723</v>
+        <v>6650785</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6316,12 +6211,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6330,7 +6225,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6352,13 +6246,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009165</t>
+          <t>https://artportalen.se/Sighting/69915522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>80009166</v>
+        <v>69915523</v>
       </c>
       <c r="B47" t="n">
         <v>43426</v>
@@ -6414,10 +6308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620840</v>
+        <v>620809</v>
       </c>
       <c r="R47" t="n">
-        <v>6650737</v>
+        <v>6650798</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6444,12 +6338,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6458,7 +6352,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6480,13 +6373,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009166</t>
+          <t>https://artportalen.se/Sighting/69915523</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>80009167</v>
+        <v>80003798</v>
       </c>
       <c r="B48" t="n">
         <v>43426</v>
@@ -6545,7 +6438,7 @@
         <v>620839</v>
       </c>
       <c r="R48" t="n">
-        <v>6650754</v>
+        <v>6650756</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6572,12 +6465,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6608,13 +6501,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009167</t>
+          <t>https://artportalen.se/Sighting/80003798</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>80009168</v>
+        <v>80003800</v>
       </c>
       <c r="B49" t="n">
         <v>43426</v>
@@ -6670,10 +6563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620838</v>
+        <v>620819</v>
       </c>
       <c r="R49" t="n">
-        <v>6650764</v>
+        <v>6650773</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6700,12 +6593,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6736,13 +6629,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009168</t>
+          <t>https://artportalen.se/Sighting/80003800</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>80009169</v>
+        <v>80003809</v>
       </c>
       <c r="B50" t="n">
         <v>43426</v>
@@ -6798,10 +6691,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620838</v>
+        <v>620769</v>
       </c>
       <c r="R50" t="n">
-        <v>6650763</v>
+        <v>6651010</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6828,12 +6721,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6864,13 +6757,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009169</t>
+          <t>https://artportalen.se/Sighting/80003809</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80009170</v>
+        <v>80003810</v>
       </c>
       <c r="B51" t="n">
         <v>43426</v>
@@ -6926,10 +6819,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620838</v>
+        <v>620769</v>
       </c>
       <c r="R51" t="n">
-        <v>6650762</v>
+        <v>6651003</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6956,12 +6849,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6992,13 +6885,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009170</t>
+          <t>https://artportalen.se/Sighting/80003810</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>80009171</v>
+        <v>80009164</v>
       </c>
       <c r="B52" t="n">
         <v>43426</v>
@@ -7028,7 +6921,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7054,10 +6947,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620838</v>
+        <v>620845</v>
       </c>
       <c r="R52" t="n">
-        <v>6650755</v>
+        <v>6650723</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7120,13 +7013,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009171</t>
+          <t>https://artportalen.se/Sighting/80009164</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>80009172</v>
+        <v>80009165</v>
       </c>
       <c r="B53" t="n">
         <v>43426</v>
@@ -7182,10 +7075,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620819</v>
+        <v>620844</v>
       </c>
       <c r="R53" t="n">
-        <v>6650772</v>
+        <v>6650723</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7248,13 +7141,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009172</t>
+          <t>https://artportalen.se/Sighting/80009165</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>80009173</v>
+        <v>80009166</v>
       </c>
       <c r="B54" t="n">
         <v>43426</v>
@@ -7310,10 +7203,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620818</v>
+        <v>620840</v>
       </c>
       <c r="R54" t="n">
-        <v>6650773</v>
+        <v>6650737</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7376,13 +7269,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009173</t>
+          <t>https://artportalen.se/Sighting/80009166</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80009174</v>
+        <v>80009167</v>
       </c>
       <c r="B55" t="n">
         <v>43426</v>
@@ -7438,10 +7331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620812</v>
+        <v>620839</v>
       </c>
       <c r="R55" t="n">
-        <v>6650789</v>
+        <v>6650754</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7504,13 +7397,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009174</t>
+          <t>https://artportalen.se/Sighting/80009167</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80009199</v>
+        <v>80009168</v>
       </c>
       <c r="B56" t="n">
         <v>43426</v>
@@ -7566,10 +7459,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>620785</v>
+        <v>620838</v>
       </c>
       <c r="R56" t="n">
-        <v>6650920</v>
+        <v>6650764</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7632,13 +7525,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009199</t>
+          <t>https://artportalen.se/Sighting/80009168</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80009200</v>
+        <v>80009169</v>
       </c>
       <c r="B57" t="n">
         <v>43426</v>
@@ -7694,10 +7587,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>620784</v>
+        <v>620838</v>
       </c>
       <c r="R57" t="n">
-        <v>6650920</v>
+        <v>6650763</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7760,13 +7653,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009200</t>
+          <t>https://artportalen.se/Sighting/80009169</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>80009201</v>
+        <v>80009170</v>
       </c>
       <c r="B58" t="n">
         <v>43426</v>
@@ -7822,10 +7715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>620777</v>
+        <v>620838</v>
       </c>
       <c r="R58" t="n">
-        <v>6650982</v>
+        <v>6650762</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7888,13 +7781,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009201</t>
+          <t>https://artportalen.se/Sighting/80009170</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>80009202</v>
+        <v>80009171</v>
       </c>
       <c r="B59" t="n">
         <v>43426</v>
@@ -7924,7 +7817,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7950,10 +7843,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>620776</v>
+        <v>620838</v>
       </c>
       <c r="R59" t="n">
-        <v>6650980</v>
+        <v>6650755</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8016,13 +7909,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009202</t>
+          <t>https://artportalen.se/Sighting/80009171</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80009203</v>
+        <v>80009172</v>
       </c>
       <c r="B60" t="n">
         <v>43426</v>
@@ -8078,10 +7971,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>620775</v>
+        <v>620819</v>
       </c>
       <c r="R60" t="n">
-        <v>6651009</v>
+        <v>6650772</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8144,13 +8037,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009203</t>
+          <t>https://artportalen.se/Sighting/80009172</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>80009204</v>
+        <v>80009173</v>
       </c>
       <c r="B61" t="n">
         <v>43426</v>
@@ -8206,10 +8099,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>620775</v>
+        <v>620818</v>
       </c>
       <c r="R61" t="n">
-        <v>6651007</v>
+        <v>6650773</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8272,13 +8165,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009204</t>
+          <t>https://artportalen.se/Sighting/80009173</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>80009205</v>
+        <v>80009174</v>
       </c>
       <c r="B62" t="n">
         <v>43426</v>
@@ -8334,10 +8227,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>620775</v>
+        <v>620812</v>
       </c>
       <c r="R62" t="n">
-        <v>6650983</v>
+        <v>6650789</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8400,13 +8293,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009205</t>
+          <t>https://artportalen.se/Sighting/80009174</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>80009208</v>
+        <v>80009199</v>
       </c>
       <c r="B63" t="n">
         <v>43426</v>
@@ -8462,10 +8355,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>620774</v>
+        <v>620785</v>
       </c>
       <c r="R63" t="n">
-        <v>6651009</v>
+        <v>6650920</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8528,13 +8421,13 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009208</t>
+          <t>https://artportalen.se/Sighting/80009199</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>80009209</v>
+        <v>80009200</v>
       </c>
       <c r="B64" t="n">
         <v>43426</v>
@@ -8590,10 +8483,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>620774</v>
+        <v>620784</v>
       </c>
       <c r="R64" t="n">
-        <v>6650978</v>
+        <v>6650920</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8656,13 +8549,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009209</t>
+          <t>https://artportalen.se/Sighting/80009200</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>80009210</v>
+        <v>80009201</v>
       </c>
       <c r="B65" t="n">
         <v>43426</v>
@@ -8718,10 +8611,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>620774</v>
+        <v>620777</v>
       </c>
       <c r="R65" t="n">
-        <v>6650976</v>
+        <v>6650982</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8784,13 +8677,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009210</t>
+          <t>https://artportalen.se/Sighting/80009201</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>80009211</v>
+        <v>80009202</v>
       </c>
       <c r="B66" t="n">
         <v>43426</v>
@@ -8846,10 +8739,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>620773</v>
+        <v>620776</v>
       </c>
       <c r="R66" t="n">
-        <v>6651009</v>
+        <v>6650980</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8912,13 +8805,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009211</t>
+          <t>https://artportalen.se/Sighting/80009202</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>80009212</v>
+        <v>80009203</v>
       </c>
       <c r="B67" t="n">
         <v>43426</v>
@@ -8974,10 +8867,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>620769</v>
+        <v>620775</v>
       </c>
       <c r="R67" t="n">
-        <v>6651006</v>
+        <v>6651009</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9040,13 +8933,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009212</t>
+          <t>https://artportalen.se/Sighting/80009203</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>80009213</v>
+        <v>80009204</v>
       </c>
       <c r="B68" t="n">
         <v>43426</v>
@@ -9102,10 +8995,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>620768</v>
+        <v>620775</v>
       </c>
       <c r="R68" t="n">
-        <v>6651009</v>
+        <v>6651007</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9168,13 +9061,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009213</t>
+          <t>https://artportalen.se/Sighting/80009204</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>80009215</v>
+        <v>80009205</v>
       </c>
       <c r="B69" t="n">
         <v>43426</v>
@@ -9204,7 +9097,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9230,10 +9123,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>620768</v>
+        <v>620775</v>
       </c>
       <c r="R69" t="n">
-        <v>6651006</v>
+        <v>6650983</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9296,13 +9189,13 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009215</t>
+          <t>https://artportalen.se/Sighting/80009205</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>80009217</v>
+        <v>80009208</v>
       </c>
       <c r="B70" t="n">
         <v>43426</v>
@@ -9358,10 +9251,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>620767</v>
+        <v>620774</v>
       </c>
       <c r="R70" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9424,13 +9317,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009217</t>
+          <t>https://artportalen.se/Sighting/80009208</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>80009218</v>
+        <v>80009209</v>
       </c>
       <c r="B71" t="n">
         <v>43426</v>
@@ -9486,10 +9379,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>620767</v>
+        <v>620774</v>
       </c>
       <c r="R71" t="n">
-        <v>6651007</v>
+        <v>6650978</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9552,13 +9445,13 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80009218</t>
+          <t>https://artportalen.se/Sighting/80009209</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>88452912</v>
+        <v>80009210</v>
       </c>
       <c r="B72" t="n">
         <v>43426</v>
@@ -9614,10 +9507,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>620848</v>
+        <v>620774</v>
       </c>
       <c r="R72" t="n">
-        <v>6650718</v>
+        <v>6650976</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9644,12 +9537,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9680,13 +9573,13 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452912</t>
+          <t>https://artportalen.se/Sighting/80009210</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>88452915</v>
+        <v>80009211</v>
       </c>
       <c r="B73" t="n">
         <v>43426</v>
@@ -9742,10 +9635,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>620819</v>
+        <v>620773</v>
       </c>
       <c r="R73" t="n">
-        <v>6650770</v>
+        <v>6651009</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9772,12 +9665,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9808,13 +9701,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452915</t>
+          <t>https://artportalen.se/Sighting/80009211</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>88452949</v>
+        <v>80009212</v>
       </c>
       <c r="B74" t="n">
         <v>43426</v>
@@ -9870,10 +9763,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>620785</v>
+        <v>620769</v>
       </c>
       <c r="R74" t="n">
-        <v>6650921</v>
+        <v>6651006</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9900,12 +9793,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9936,13 +9829,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452949</t>
+          <t>https://artportalen.se/Sighting/80009212</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>88452955</v>
+        <v>80009213</v>
       </c>
       <c r="B75" t="n">
         <v>43426</v>
@@ -9998,10 +9891,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>620779</v>
+        <v>620768</v>
       </c>
       <c r="R75" t="n">
-        <v>6650984</v>
+        <v>6651009</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -10028,17 +9921,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Slåtteryta söder om Siggeforasjön.</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10069,13 +9957,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452955</t>
+          <t>https://artportalen.se/Sighting/80009213</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88452957</v>
+        <v>80009215</v>
       </c>
       <c r="B76" t="n">
         <v>43426</v>
@@ -10105,7 +9993,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10131,10 +10019,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>620778</v>
+        <v>620768</v>
       </c>
       <c r="R76" t="n">
-        <v>6650984</v>
+        <v>6651006</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10161,17 +10049,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Slåtteryta söder om Siggeforasjön.</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10202,13 +10085,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452957</t>
+          <t>https://artportalen.se/Sighting/80009215</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>88452959</v>
+        <v>80009217</v>
       </c>
       <c r="B77" t="n">
         <v>43426</v>
@@ -10264,10 +10147,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>620774</v>
+        <v>620767</v>
       </c>
       <c r="R77" t="n">
-        <v>6651010</v>
+        <v>6651008</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10294,17 +10177,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Slåtteryta söder om Siggeforasjön.</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10335,13 +10213,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452959</t>
+          <t>https://artportalen.se/Sighting/80009217</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>88452960</v>
+        <v>80009218</v>
       </c>
       <c r="B78" t="n">
         <v>43426</v>
@@ -10397,10 +10275,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>620773</v>
+        <v>620767</v>
       </c>
       <c r="R78" t="n">
-        <v>6651006</v>
+        <v>6651007</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10427,17 +10305,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Slåtteryta söder om Siggeforasjön.</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10468,13 +10341,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88452960</t>
+          <t>https://artportalen.se/Sighting/80009218</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>96910873</v>
+        <v>88452912</v>
       </c>
       <c r="B79" t="n">
         <v>43426</v>
@@ -10530,10 +10403,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>620838</v>
+        <v>620848</v>
       </c>
       <c r="R79" t="n">
-        <v>6650754</v>
+        <v>6650718</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10560,12 +10433,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10596,13 +10469,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910873</t>
+          <t>https://artportalen.se/Sighting/88452912</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>96910874</v>
+        <v>88452915</v>
       </c>
       <c r="B80" t="n">
         <v>43426</v>
@@ -10658,10 +10531,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>620833</v>
+        <v>620819</v>
       </c>
       <c r="R80" t="n">
-        <v>6650755</v>
+        <v>6650770</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10688,12 +10561,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10724,13 +10597,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910874</t>
+          <t>https://artportalen.se/Sighting/88452915</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>96910875</v>
+        <v>88452949</v>
       </c>
       <c r="B81" t="n">
         <v>43426</v>
@@ -10786,10 +10659,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>620823</v>
+        <v>620785</v>
       </c>
       <c r="R81" t="n">
-        <v>6650713</v>
+        <v>6650921</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10816,17 +10689,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På transportvägen (grusvägen)</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10857,13 +10725,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910875</t>
+          <t>https://artportalen.se/Sighting/88452949</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>96910876</v>
+        <v>88452955</v>
       </c>
       <c r="B82" t="n">
         <v>43426</v>
@@ -10919,10 +10787,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>620821</v>
+        <v>620779</v>
       </c>
       <c r="R82" t="n">
-        <v>6650773</v>
+        <v>6650984</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10949,12 +10817,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Slåtteryta söder om Siggeforasjön.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10985,13 +10858,13 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910876</t>
+          <t>https://artportalen.se/Sighting/88452955</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>96910877</v>
+        <v>88452957</v>
       </c>
       <c r="B83" t="n">
         <v>43426</v>
@@ -11047,10 +10920,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>620821</v>
+        <v>620778</v>
       </c>
       <c r="R83" t="n">
-        <v>6650772</v>
+        <v>6650984</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11077,12 +10950,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Slåtteryta söder om Siggeforasjön.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11113,13 +10991,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910877</t>
+          <t>https://artportalen.se/Sighting/88452957</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96910882</v>
+        <v>88452959</v>
       </c>
       <c r="B84" t="n">
         <v>43426</v>
@@ -11175,10 +11053,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>620779</v>
+        <v>620774</v>
       </c>
       <c r="R84" t="n">
-        <v>6650986</v>
+        <v>6651010</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -11205,17 +11083,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Slåtteryta söder om Siggeforasjön</t>
+          <t>Slåtteryta söder om Siggeforasjön.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11246,13 +11124,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910882</t>
+          <t>https://artportalen.se/Sighting/88452959</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>96910883</v>
+        <v>88452960</v>
       </c>
       <c r="B85" t="n">
         <v>43426</v>
@@ -11308,10 +11186,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>620777</v>
+        <v>620773</v>
       </c>
       <c r="R85" t="n">
-        <v>6650985</v>
+        <v>6651006</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -11338,17 +11216,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Slåtteryta söder om Siggeforasjön</t>
+          <t>Slåtteryta söder om Siggeforasjön.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11379,13 +11257,13 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910883</t>
+          <t>https://artportalen.se/Sighting/88452960</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>96910884</v>
+        <v>96910873</v>
       </c>
       <c r="B86" t="n">
         <v>43426</v>
@@ -11441,10 +11319,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>620776</v>
+        <v>620838</v>
       </c>
       <c r="R86" t="n">
-        <v>6650978</v>
+        <v>6650754</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11479,11 +11357,6 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Slåtteryta söder om Siggeforasjön</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -11512,13 +11385,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96910884</t>
+          <t>https://artportalen.se/Sighting/96910873</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>104399855</v>
+        <v>96910874</v>
       </c>
       <c r="B87" t="n">
         <v>43426</v>
@@ -11574,10 +11447,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>620822</v>
+        <v>620833</v>
       </c>
       <c r="R87" t="n">
-        <v>6650715</v>
+        <v>6650755</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11604,17 +11477,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På transportvägen (grusvägen)</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11645,13 +11513,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104399855</t>
+          <t>https://artportalen.se/Sighting/96910874</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>104399856</v>
+        <v>96910875</v>
       </c>
       <c r="B88" t="n">
         <v>43426</v>
@@ -11707,10 +11575,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>620822</v>
+        <v>620823</v>
       </c>
       <c r="R88" t="n">
-        <v>6650714</v>
+        <v>6650713</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11737,12 +11605,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -11778,13 +11646,13 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104399856</t>
+          <t>https://artportalen.se/Sighting/96910875</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104400071</v>
+        <v>96910876</v>
       </c>
       <c r="B89" t="n">
         <v>43426</v>
@@ -11840,10 +11708,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>620843</v>
+        <v>620821</v>
       </c>
       <c r="R89" t="n">
-        <v>6650758</v>
+        <v>6650773</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11870,12 +11738,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11906,13 +11774,13 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400071</t>
+          <t>https://artportalen.se/Sighting/96910876</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>104400072</v>
+        <v>96910877</v>
       </c>
       <c r="B90" t="n">
         <v>43426</v>
@@ -11968,10 +11836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>620842</v>
+        <v>620821</v>
       </c>
       <c r="R90" t="n">
-        <v>6650757</v>
+        <v>6650772</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -11998,12 +11866,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12034,13 +11902,13 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400072</t>
+          <t>https://artportalen.se/Sighting/96910877</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>104400073</v>
+        <v>96910882</v>
       </c>
       <c r="B91" t="n">
         <v>43426</v>
@@ -12096,10 +11964,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>620840</v>
+        <v>620779</v>
       </c>
       <c r="R91" t="n">
-        <v>6650728</v>
+        <v>6650986</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12126,12 +11994,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Slåtteryta söder om Siggeforasjön</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12162,13 +12035,13 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400073</t>
+          <t>https://artportalen.se/Sighting/96910882</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>104400074</v>
+        <v>96910883</v>
       </c>
       <c r="B92" t="n">
         <v>43426</v>
@@ -12224,10 +12097,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>620839</v>
+        <v>620777</v>
       </c>
       <c r="R92" t="n">
-        <v>6650755</v>
+        <v>6650985</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -12254,12 +12127,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Slåtteryta söder om Siggeforasjön</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12290,13 +12168,13 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400074</t>
+          <t>https://artportalen.se/Sighting/96910883</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>104400075</v>
+        <v>96910884</v>
       </c>
       <c r="B93" t="n">
         <v>43426</v>
@@ -12352,10 +12230,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>620836</v>
+        <v>620776</v>
       </c>
       <c r="R93" t="n">
-        <v>6650755</v>
+        <v>6650978</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -12382,12 +12260,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Slåtteryta söder om Siggeforasjön</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12418,13 +12301,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400075</t>
+          <t>https://artportalen.se/Sighting/96910884</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104400076</v>
+        <v>104399855</v>
       </c>
       <c r="B94" t="n">
         <v>43426</v>
@@ -12480,10 +12363,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>620836</v>
+        <v>620822</v>
       </c>
       <c r="R94" t="n">
-        <v>6650750</v>
+        <v>6650715</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -12518,6 +12401,11 @@
           <t>2022-08-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På transportvägen (grusvägen)</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12546,13 +12434,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400076</t>
+          <t>https://artportalen.se/Sighting/104399855</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>104400077</v>
+        <v>104399856</v>
       </c>
       <c r="B95" t="n">
         <v>43426</v>
@@ -12608,10 +12496,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>620835</v>
+        <v>620822</v>
       </c>
       <c r="R95" t="n">
-        <v>6650754</v>
+        <v>6650714</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -12646,6 +12534,11 @@
           <t>2022-08-26</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På transportvägen (grusvägen)</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -12674,13 +12567,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400077</t>
+          <t>https://artportalen.se/Sighting/104399856</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104400078</v>
+        <v>104400071</v>
       </c>
       <c r="B96" t="n">
         <v>43426</v>
@@ -12736,10 +12629,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>620827</v>
+        <v>620843</v>
       </c>
       <c r="R96" t="n">
-        <v>6650775</v>
+        <v>6650758</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -12802,13 +12695,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400078</t>
+          <t>https://artportalen.se/Sighting/104400071</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>104400079</v>
+        <v>104400072</v>
       </c>
       <c r="B97" t="n">
         <v>43426</v>
@@ -12864,10 +12757,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>620811</v>
+        <v>620842</v>
       </c>
       <c r="R97" t="n">
-        <v>6650790</v>
+        <v>6650757</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12930,13 +12823,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400079</t>
+          <t>https://artportalen.se/Sighting/104400072</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>104400089</v>
+        <v>104400073</v>
       </c>
       <c r="B98" t="n">
         <v>43426</v>
@@ -12992,10 +12885,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>620777</v>
+        <v>620840</v>
       </c>
       <c r="R98" t="n">
-        <v>6650977</v>
+        <v>6650728</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -13058,13 +12951,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400089</t>
+          <t>https://artportalen.se/Sighting/104400073</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>104400091</v>
+        <v>104400074</v>
       </c>
       <c r="B99" t="n">
         <v>43426</v>
@@ -13120,10 +13013,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>620776</v>
+        <v>620839</v>
       </c>
       <c r="R99" t="n">
-        <v>6650977</v>
+        <v>6650755</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -13186,13 +13079,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400091</t>
+          <t>https://artportalen.se/Sighting/104400074</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>104400095</v>
+        <v>104400075</v>
       </c>
       <c r="B100" t="n">
         <v>43426</v>
@@ -13248,10 +13141,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>620767</v>
+        <v>620836</v>
       </c>
       <c r="R100" t="n">
-        <v>6651012</v>
+        <v>6650755</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -13314,13 +13207,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400095</t>
+          <t>https://artportalen.se/Sighting/104400075</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>104400096</v>
+        <v>104400076</v>
       </c>
       <c r="B101" t="n">
         <v>43426</v>
@@ -13376,10 +13269,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>620767</v>
+        <v>620836</v>
       </c>
       <c r="R101" t="n">
-        <v>6651011</v>
+        <v>6650750</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -13442,13 +13335,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104400096</t>
+          <t>https://artportalen.se/Sighting/104400076</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110017553</v>
+        <v>104400077</v>
       </c>
       <c r="B102" t="n">
         <v>43426</v>
@@ -13481,24 +13374,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Södra ledningsgatan, Siggefora, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>620784</v>
+        <v>620835</v>
       </c>
       <c r="R102" t="n">
-        <v>6650931</v>
+        <v>6650754</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13522,12 +13427,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13536,30 +13441,35 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Mikael Åsberg</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110017553</t>
+          <t>https://artportalen.se/Sighting/104400077</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>113321512</v>
+        <v>104400078</v>
       </c>
       <c r="B103" t="n">
         <v>43426</v>
@@ -13615,10 +13525,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>620779</v>
+        <v>620827</v>
       </c>
       <c r="R103" t="n">
-        <v>6651007</v>
+        <v>6650775</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -13645,12 +13555,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13681,13 +13591,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321512</t>
+          <t>https://artportalen.se/Sighting/104400078</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>113321513</v>
+        <v>104400079</v>
       </c>
       <c r="B104" t="n">
         <v>43426</v>
@@ -13743,10 +13653,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>620780</v>
+        <v>620811</v>
       </c>
       <c r="R104" t="n">
-        <v>6650980</v>
+        <v>6650790</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -13773,12 +13683,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13809,13 +13719,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321513</t>
+          <t>https://artportalen.se/Sighting/104400079</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>113321514</v>
+        <v>104400089</v>
       </c>
       <c r="B105" t="n">
         <v>43426</v>
@@ -13871,10 +13781,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>620778</v>
+        <v>620777</v>
       </c>
       <c r="R105" t="n">
-        <v>6650983</v>
+        <v>6650977</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -13901,12 +13811,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13937,13 +13847,13 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321514</t>
+          <t>https://artportalen.se/Sighting/104400089</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>113321515</v>
+        <v>104400091</v>
       </c>
       <c r="B106" t="n">
         <v>43426</v>
@@ -13999,10 +13909,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>620779</v>
+        <v>620776</v>
       </c>
       <c r="R106" t="n">
-        <v>6650981</v>
+        <v>6650977</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -14029,12 +13939,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14065,13 +13975,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321515</t>
+          <t>https://artportalen.se/Sighting/104400091</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>113321516</v>
+        <v>104400095</v>
       </c>
       <c r="B107" t="n">
         <v>43426</v>
@@ -14127,10 +14037,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>620787</v>
+        <v>620767</v>
       </c>
       <c r="R107" t="n">
-        <v>6650915</v>
+        <v>6651012</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -14157,12 +14067,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14193,13 +14103,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321516</t>
+          <t>https://artportalen.se/Sighting/104400095</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>113321535</v>
+        <v>104400096</v>
       </c>
       <c r="B108" t="n">
         <v>43426</v>
@@ -14255,10 +14165,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>620841</v>
+        <v>620767</v>
       </c>
       <c r="R108" t="n">
-        <v>6650730</v>
+        <v>6651011</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -14285,12 +14195,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14321,13 +14231,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321535</t>
+          <t>https://artportalen.se/Sighting/104400096</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>113321536</v>
+        <v>110017553</v>
       </c>
       <c r="B109" t="n">
         <v>43426</v>
@@ -14360,36 +14270,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Siggefora ledningsgata, Upl</t>
+          <t>Södra ledningsgatan, Siggefora, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>620846</v>
+        <v>620784</v>
       </c>
       <c r="R109" t="n">
-        <v>6650734</v>
+        <v>6650931</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14413,12 +14311,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14427,35 +14325,30 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Mikael Åsberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321536</t>
+          <t>https://artportalen.se/Sighting/110017553</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>113321537</v>
+        <v>113321512</v>
       </c>
       <c r="B110" t="n">
         <v>43426</v>
@@ -14511,10 +14404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>620837</v>
+        <v>620779</v>
       </c>
       <c r="R110" t="n">
-        <v>6650748</v>
+        <v>6651007</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -14577,13 +14470,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321537</t>
+          <t>https://artportalen.se/Sighting/113321512</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>113321538</v>
+        <v>113321513</v>
       </c>
       <c r="B111" t="n">
         <v>43426</v>
@@ -14639,10 +14532,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>620837</v>
+        <v>620780</v>
       </c>
       <c r="R111" t="n">
-        <v>6650759</v>
+        <v>6650980</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -14705,13 +14598,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321538</t>
+          <t>https://artportalen.se/Sighting/113321513</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>113321539</v>
+        <v>113321514</v>
       </c>
       <c r="B112" t="n">
         <v>43426</v>
@@ -14767,10 +14660,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>620836</v>
+        <v>620778</v>
       </c>
       <c r="R112" t="n">
-        <v>6650756</v>
+        <v>6650983</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -14833,13 +14726,13 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321539</t>
+          <t>https://artportalen.se/Sighting/113321514</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>113321540</v>
+        <v>113321515</v>
       </c>
       <c r="B113" t="n">
         <v>43426</v>
@@ -14895,10 +14788,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>620836</v>
+        <v>620779</v>
       </c>
       <c r="R113" t="n">
-        <v>6650754</v>
+        <v>6650981</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -14961,13 +14854,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321540</t>
+          <t>https://artportalen.se/Sighting/113321515</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>113321541</v>
+        <v>113321516</v>
       </c>
       <c r="B114" t="n">
         <v>43426</v>
@@ -15023,10 +14916,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>620839</v>
+        <v>620787</v>
       </c>
       <c r="R114" t="n">
-        <v>6650759</v>
+        <v>6650915</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -15089,13 +14982,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321541</t>
+          <t>https://artportalen.se/Sighting/113321516</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>113321542</v>
+        <v>113321535</v>
       </c>
       <c r="B115" t="n">
         <v>43426</v>
@@ -15151,10 +15044,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>620819</v>
+        <v>620841</v>
       </c>
       <c r="R115" t="n">
-        <v>6650776</v>
+        <v>6650730</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -15217,13 +15110,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321542</t>
+          <t>https://artportalen.se/Sighting/113321535</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>113321547</v>
+        <v>113321536</v>
       </c>
       <c r="B116" t="n">
         <v>43426</v>
@@ -15279,10 +15172,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>620787</v>
+        <v>620846</v>
       </c>
       <c r="R116" t="n">
-        <v>6650919</v>
+        <v>6650734</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -15345,13 +15238,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321547</t>
+          <t>https://artportalen.se/Sighting/113321536</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>113321548</v>
+        <v>113321537</v>
       </c>
       <c r="B117" t="n">
         <v>43426</v>
@@ -15407,10 +15300,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>620785</v>
+        <v>620837</v>
       </c>
       <c r="R117" t="n">
-        <v>6650922</v>
+        <v>6650748</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -15473,13 +15366,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321548</t>
+          <t>https://artportalen.se/Sighting/113321537</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>113321549</v>
+        <v>113321538</v>
       </c>
       <c r="B118" t="n">
         <v>43426</v>
@@ -15535,10 +15428,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>620783</v>
+        <v>620837</v>
       </c>
       <c r="R118" t="n">
-        <v>6650924</v>
+        <v>6650759</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -15601,13 +15494,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321549</t>
+          <t>https://artportalen.se/Sighting/113321538</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>113321550</v>
+        <v>113321539</v>
       </c>
       <c r="B119" t="n">
         <v>43426</v>
@@ -15663,10 +15556,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>620784</v>
+        <v>620836</v>
       </c>
       <c r="R119" t="n">
-        <v>6650925</v>
+        <v>6650756</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -15729,13 +15622,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321550</t>
+          <t>https://artportalen.se/Sighting/113321539</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>113321551</v>
+        <v>113321540</v>
       </c>
       <c r="B120" t="n">
         <v>43426</v>
@@ -15791,10 +15684,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>620785</v>
+        <v>620836</v>
       </c>
       <c r="R120" t="n">
-        <v>6650927</v>
+        <v>6650754</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -15857,13 +15750,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321551</t>
+          <t>https://artportalen.se/Sighting/113321540</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113321552</v>
+        <v>113321541</v>
       </c>
       <c r="B121" t="n">
         <v>43426</v>
@@ -15919,10 +15812,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620784</v>
+        <v>620839</v>
       </c>
       <c r="R121" t="n">
-        <v>6650933</v>
+        <v>6650759</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -15985,13 +15878,13 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321552</t>
+          <t>https://artportalen.se/Sighting/113321541</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>113321553</v>
+        <v>113321542</v>
       </c>
       <c r="B122" t="n">
         <v>43426</v>
@@ -16047,10 +15940,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620784</v>
+        <v>620819</v>
       </c>
       <c r="R122" t="n">
-        <v>6650932</v>
+        <v>6650776</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -16113,13 +16006,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113321553</t>
+          <t>https://artportalen.se/Sighting/113321542</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120777183</v>
+        <v>113321547</v>
       </c>
       <c r="B123" t="n">
         <v>43426</v>
@@ -16175,10 +16068,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620779</v>
+        <v>620787</v>
       </c>
       <c r="R123" t="n">
-        <v>6651011</v>
+        <v>6650919</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -16205,12 +16098,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16241,13 +16134,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777183</t>
+          <t>https://artportalen.se/Sighting/113321547</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120777184</v>
+        <v>113321548</v>
       </c>
       <c r="B124" t="n">
         <v>43426</v>
@@ -16303,10 +16196,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620773</v>
+        <v>620785</v>
       </c>
       <c r="R124" t="n">
-        <v>6651010</v>
+        <v>6650922</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -16333,12 +16226,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16369,13 +16262,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777184</t>
+          <t>https://artportalen.se/Sighting/113321548</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120777190</v>
+        <v>113321549</v>
       </c>
       <c r="B125" t="n">
         <v>43426</v>
@@ -16431,10 +16324,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>620767</v>
+        <v>620783</v>
       </c>
       <c r="R125" t="n">
-        <v>6651010</v>
+        <v>6650924</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -16461,12 +16354,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16497,13 +16390,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777190</t>
+          <t>https://artportalen.se/Sighting/113321549</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120777191</v>
+        <v>113321550</v>
       </c>
       <c r="B126" t="n">
         <v>43426</v>
@@ -16559,10 +16452,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>620781</v>
+        <v>620784</v>
       </c>
       <c r="R126" t="n">
-        <v>6650985</v>
+        <v>6650925</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -16589,12 +16482,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16625,13 +16518,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777191</t>
+          <t>https://artportalen.se/Sighting/113321550</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120777193</v>
+        <v>113321551</v>
       </c>
       <c r="B127" t="n">
         <v>43426</v>
@@ -16687,10 +16580,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>620778</v>
+        <v>620785</v>
       </c>
       <c r="R127" t="n">
-        <v>6650988</v>
+        <v>6650927</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -16717,12 +16610,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16753,13 +16646,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777193</t>
+          <t>https://artportalen.se/Sighting/113321551</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120777195</v>
+        <v>113321552</v>
       </c>
       <c r="B128" t="n">
         <v>43426</v>
@@ -16815,10 +16708,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>620776</v>
+        <v>620784</v>
       </c>
       <c r="R128" t="n">
-        <v>6650986</v>
+        <v>6650933</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -16845,12 +16738,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16881,13 +16774,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777195</t>
+          <t>https://artportalen.se/Sighting/113321552</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120777196</v>
+        <v>113321553</v>
       </c>
       <c r="B129" t="n">
         <v>43426</v>
@@ -16943,10 +16836,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>620780</v>
+        <v>620784</v>
       </c>
       <c r="R129" t="n">
-        <v>6650985</v>
+        <v>6650932</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16973,12 +16866,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -17009,13 +16902,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777196</t>
+          <t>https://artportalen.se/Sighting/113321553</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120777198</v>
+        <v>120777183</v>
       </c>
       <c r="B130" t="n">
         <v>43426</v>
@@ -17071,10 +16964,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>620774</v>
+        <v>620779</v>
       </c>
       <c r="R130" t="n">
-        <v>6650981</v>
+        <v>6651011</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -17137,13 +17030,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777198</t>
+          <t>https://artportalen.se/Sighting/120777183</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120777199</v>
+        <v>120777184</v>
       </c>
       <c r="B131" t="n">
         <v>43426</v>
@@ -17199,10 +17092,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>620776</v>
+        <v>620773</v>
       </c>
       <c r="R131" t="n">
-        <v>6650982</v>
+        <v>6651010</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -17265,13 +17158,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777199</t>
+          <t>https://artportalen.se/Sighting/120777184</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120777202</v>
+        <v>120777190</v>
       </c>
       <c r="B132" t="n">
         <v>43426</v>
@@ -17327,10 +17220,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>620782</v>
+        <v>620767</v>
       </c>
       <c r="R132" t="n">
-        <v>6650936</v>
+        <v>6651010</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -17393,13 +17286,13 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777202</t>
+          <t>https://artportalen.se/Sighting/120777190</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120777207</v>
+        <v>120777191</v>
       </c>
       <c r="B133" t="n">
         <v>43426</v>
@@ -17455,10 +17348,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>620837</v>
+        <v>620781</v>
       </c>
       <c r="R133" t="n">
-        <v>6650762</v>
+        <v>6650985</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -17521,13 +17414,13 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120777207</t>
+          <t>https://artportalen.se/Sighting/120777191</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129619331</v>
+        <v>120777193</v>
       </c>
       <c r="B134" t="n">
         <v>43426</v>
@@ -17583,10 +17476,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>620781</v>
+        <v>620778</v>
       </c>
       <c r="R134" t="n">
-        <v>6650986</v>
+        <v>6650988</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -17613,12 +17506,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17649,13 +17542,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129619331</t>
+          <t>https://artportalen.se/Sighting/120777193</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129619334</v>
+        <v>120777195</v>
       </c>
       <c r="B135" t="n">
         <v>43426</v>
@@ -17711,10 +17604,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>620773</v>
+        <v>620776</v>
       </c>
       <c r="R135" t="n">
-        <v>6651008</v>
+        <v>6650986</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -17741,12 +17634,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17777,16 +17670,16 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129619334</t>
+          <t>https://artportalen.se/Sighting/120777195</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136624956</v>
+        <v>120777196</v>
       </c>
       <c r="B136" t="n">
-        <v>43459</v>
+        <v>43426</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17811,8 +17704,16 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -17820,20 +17721,24 @@
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Uppsala Län, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>620777</v>
+        <v>620780</v>
       </c>
       <c r="R136" t="n">
-        <v>6650974</v>
+        <v>6650985</v>
       </c>
       <c r="S136" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17857,12 +17762,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17878,31 +17783,31 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136624956</t>
+          <t>https://artportalen.se/Sighting/120777196</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136624962</v>
+        <v>120777198</v>
       </c>
       <c r="B137" t="n">
-        <v>43459</v>
+        <v>43426</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17927,8 +17832,16 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -17936,20 +17849,24 @@
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Uppsala Län, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>620780</v>
+        <v>620774</v>
       </c>
       <c r="R137" t="n">
-        <v>6651005</v>
+        <v>6650981</v>
       </c>
       <c r="S137" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17973,12 +17890,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17994,31 +17911,31 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136624962</t>
+          <t>https://artportalen.se/Sighting/120777198</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>136624963</v>
+        <v>120777199</v>
       </c>
       <c r="B138" t="n">
-        <v>43459</v>
+        <v>43426</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18043,8 +17960,16 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -18052,20 +17977,24 @@
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Uppsala Län, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>620775</v>
+        <v>620776</v>
       </c>
       <c r="R138" t="n">
-        <v>6651011</v>
+        <v>6650982</v>
       </c>
       <c r="S138" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -18089,12 +18018,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18110,31 +18039,31 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136624963</t>
+          <t>https://artportalen.se/Sighting/120777199</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136624968</v>
+        <v>120777202</v>
       </c>
       <c r="B139" t="n">
-        <v>43459</v>
+        <v>43426</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18159,8 +18088,16 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -18168,20 +18105,24 @@
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Uppsala Län, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>620770</v>
+        <v>620782</v>
       </c>
       <c r="R139" t="n">
-        <v>6651009</v>
+        <v>6650936</v>
       </c>
       <c r="S139" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -18205,12 +18146,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18226,31 +18167,31 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136624968</t>
+          <t>https://artportalen.se/Sighting/120777202</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136624970</v>
+        <v>120777207</v>
       </c>
       <c r="B140" t="n">
-        <v>43459</v>
+        <v>43426</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18275,8 +18216,16 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>larv/nymf</t>
@@ -18284,20 +18233,24 @@
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Uppsala Län, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>620770</v>
+        <v>620837</v>
       </c>
       <c r="R140" t="n">
-        <v>6651006</v>
+        <v>6650762</v>
       </c>
       <c r="S140" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -18321,12 +18274,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18342,53 +18295,53 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136624970</t>
+          <t>https://artportalen.se/Sighting/120777207</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>110017543</v>
+        <v>129619331</v>
       </c>
       <c r="B141" t="n">
-        <v>43438</v>
+        <v>43426</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>101298</v>
+        <v>100942</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -18396,24 +18349,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Södra ledningsgatan, Siggefora, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>620824</v>
+        <v>620781</v>
       </c>
       <c r="R141" t="n">
-        <v>6650727</v>
+        <v>6650986</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -18437,12 +18402,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18451,55 +18416,60 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Mikael Åsberg</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110017543</t>
+          <t>https://artportalen.se/Sighting/129619331</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>110016422</v>
+        <v>129619334</v>
       </c>
       <c r="B142" t="n">
-        <v>58039</v>
+        <v>43426</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102626</v>
+        <v>100942</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -18507,29 +18477,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Södra ledningsgatan, Siggefora, Upl</t>
+          <t>Siggefora ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>620810</v>
+        <v>620773</v>
       </c>
       <c r="R142" t="n">
-        <v>6650785</v>
+        <v>6651008</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -18553,12 +18530,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -18567,96 +18544,85 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Mikael Åsberg</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110016422</t>
+          <t>https://artportalen.se/Sighting/129619334</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130715501</v>
+        <v>136624956</v>
       </c>
       <c r="B143" t="n">
-        <v>5362</v>
+        <v>43459</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>105947</v>
+        <v>100942</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Större aspvedbock</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Saperda carcharias</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Siggefora, kraftledningsgatan, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>620786</v>
+        <v>620777</v>
       </c>
       <c r="R143" t="n">
-        <v>6651017</v>
+        <v>6650974</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18680,12 +18646,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18701,27 +18667,31 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Milad Avalinejad Bandari</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Rasmus Elleby, Jon Jörpeland</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130715501</t>
+          <t>https://artportalen.se/Sighting/136624956</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>60228648</v>
+        <v>136624962</v>
       </c>
       <c r="B144" t="n">
-        <v>43378</v>
+        <v>43459</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18729,54 +18699,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>201075</v>
+        <v>100942</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Siggeforasjön, Upl</t>
+          <t>Uppsala Län, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>620769</v>
+        <v>620780</v>
       </c>
       <c r="R144" t="n">
-        <v>6650998</v>
+        <v>6651005</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18800,12 +18762,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18814,22 +18776,849 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624962</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>136624963</v>
+      </c>
+      <c r="B145" t="n">
+        <v>43459</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>620775</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6651011</v>
+      </c>
+      <c r="S145" t="n">
+        <v>8</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624963</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>136624968</v>
+      </c>
+      <c r="B146" t="n">
+        <v>43459</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>620770</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6651009</v>
+      </c>
+      <c r="S146" t="n">
+        <v>8</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624968</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>136624970</v>
+      </c>
+      <c r="B147" t="n">
+        <v>43459</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>620770</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6651006</v>
+      </c>
+      <c r="S147" t="n">
+        <v>8</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624970</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>110017543</v>
+      </c>
+      <c r="B148" t="n">
+        <v>43438</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>101298</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Melitaea diamina</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Södra ledningsgatan, Siggefora, Upl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>620824</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6650727</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110017543</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>110016422</v>
+      </c>
+      <c r="B149" t="n">
+        <v>58039</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Södra ledningsgatan, Siggefora, Upl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>620810</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6650785</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Mikael Åsberg, Niclas Eklund, Moa Pettersson, Rasmus Elleby, Hans Elleby, Weine Erlandsson, Ingrid Åkerberg, Göran Frisk, Thomas Persson Vinnersten, Annika Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110016422</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>130715501</v>
+      </c>
+      <c r="B150" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>105947</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Större aspvedbock</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Saperda carcharias</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Siggefora, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>620786</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6651017</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Rasmus Elleby, Jon Jörpeland</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130715501</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>60228648</v>
+      </c>
+      <c r="B151" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Siggeforasjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>620769</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6650998</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2016-06-20</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2016-06-20</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
           <t>Göran Frisk</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
+      <c r="AX151" t="inlineStr">
         <is>
           <t>Göran Frisk, Kristina Nygren Frisk</t>
         </is>
       </c>
-      <c r="AY144" t="inlineStr"/>
-      <c r="AZ144" t="inlineStr">
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/60228648</t>
         </is>
@@ -18980,6 +19769,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -18600,7 +18600,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
@@ -18677,7 +18681,7 @@
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
@@ -18716,7 +18720,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
@@ -18793,7 +18801,7 @@
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
@@ -18832,7 +18840,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
@@ -18909,7 +18921,7 @@
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
@@ -18948,7 +18960,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
@@ -18967,7 +18983,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>
@@ -19025,7 +19041,7 @@
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
@@ -19064,7 +19080,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
@@ -19141,7 +19161,7 @@
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>136624956</v>
       </c>
       <c r="B143" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>136624962</v>
       </c>
       <c r="B144" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>136624963</v>
       </c>
       <c r="B145" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>136624968</v>
       </c>
       <c r="B146" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>136624970</v>
       </c>
       <c r="B147" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>136624956</v>
       </c>
       <c r="B143" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>136624962</v>
       </c>
       <c r="B144" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>136624963</v>
       </c>
       <c r="B145" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>136624968</v>
       </c>
       <c r="B146" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>136624970</v>
       </c>
       <c r="B147" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -1269,11 +1269,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östfora, Upl</t>
@@ -18606,11 +18602,7 @@
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
@@ -18726,11 +18718,7 @@
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
@@ -18846,11 +18834,7 @@
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
@@ -18966,11 +18950,7 @@
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
@@ -19086,11 +19066,7 @@
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136866753</v>
       </c>
       <c r="B10" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>136624956</v>
       </c>
       <c r="B143" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>136624962</v>
       </c>
       <c r="B144" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>136624963</v>
       </c>
       <c r="B145" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>136624968</v>
       </c>
       <c r="B146" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136624970</v>
       </c>
       <c r="B147" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>136624956</v>
       </c>
       <c r="B143" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>136624962</v>
       </c>
       <c r="B144" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>136624963</v>
       </c>
       <c r="B145" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>136624968</v>
       </c>
       <c r="B146" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>
@@ -19035,7 +19035,7 @@
         <v>136624970</v>
       </c>
       <c r="B147" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136866752</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -18963,7 +18963,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651008</v>
+        <v>6651009</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866751</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136866741</v>
       </c>
       <c r="B3" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136866742</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136866744</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136866746</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35306-2026 artfynd.xlsx
+++ b/artfynd/A 35306-2026 artfynd.xlsx
@@ -18963,7 +18963,7 @@
         <v>620770</v>
       </c>
       <c r="R146" t="n">
-        <v>6651009</v>
+        <v>6651008</v>
       </c>
       <c r="S146" t="n">
         <v>8</v>
